--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9256676225</v>
+        <v>46157.9309376194</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9309376194</v>
+        <v>46157.93170693933</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93170693933</v>
+        <v>46157.93398587214</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398587214</v>
+        <v>46157.93716320652</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716320652</v>
+        <v>46158.28214933976</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28214933976</v>
+        <v>46158.29676411195</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676411195</v>
+        <v>46158.29813033655</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29813033655</v>
+        <v>46158.3338590461</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3338590461</v>
+        <v>46158.3685568108</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/13. ИП Мякота Игорь (диагностика авто)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3685568108</v>
+        <v>46158.3728639277</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
